--- a/artfynd/A 10326-2024 artfynd.xlsx
+++ b/artfynd/A 10326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4366,6 +4366,234 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120403852</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>675737</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6614528</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120403850</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>675737</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6614528</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10326-2024 artfynd.xlsx
+++ b/artfynd/A 10326-2024 artfynd.xlsx
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403852</v>
+        <v>120403850</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4384,21 +4384,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403850</v>
+        <v>120403852</v>
       </c>
       <c r="B38" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,21 +4498,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
